--- a/order_forms/035_graduation_apparel_order_form_template--order_forms.xlsx
+++ b/order_forms/035_graduation_apparel_order_form_template--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cap_and_gown',_'label':_'cap-and-gown'}</t>
+          <t>cap-and-gown</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'cap_and_gown', 'label': 'cap-and-gown'}</t>
+          <t>cap-and-gown</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'graduation_annual',_'label':_'graduation-annual'}</t>
+          <t>graduation-annual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'graduation_annual', 'label': 'graduation-annual'}</t>
+          <t>graduation-annual</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'graduation_hood',_'label':_'graduation-hood'}</t>
+          <t>graduation-hood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'graduation_hood', 'label': 'graduation-hood'}</t>
+          <t>graduation-hood</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'graduation_tassel',_'label':_'graduation-tassel'}</t>
+          <t>graduation-tassel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'graduation_tassel', 'label': 'graduation-tassel'}</t>
+          <t>graduation-tassel</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'graduation_stole',_'label':_'graduation-stole'}</t>
+          <t>graduation-stole</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'graduation_stole', 'label': 'graduation-stole'}</t>
+          <t>graduation-stole</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'graduation_annual_alt',_'label':_'graduation-annual-alt'}</t>
+          <t>graduation-annual-alt</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'graduation_annual_alt', 'label': 'graduation-annual-alt'}</t>
+          <t>graduation-annual-alt</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'graduation_hood_alt',_'label':_'graduation-hood-alt'}</t>
+          <t>graduation-hood-alt</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'graduation_hood_alt', 'label': 'graduation-hood-alt'}</t>
+          <t>graduation-hood-alt</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'graduation_tassel_alt',_'label':_'graduation-tassel-alt'}</t>
+          <t>graduation-tassel-alt</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'graduation_tassel_alt', 'label': 'graduation-tassel-alt'}</t>
+          <t>graduation-tassel-alt</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'graduation_stole_alt',_'label':_'graduation-stole-alt'}</t>
+          <t>graduation-stole-alt</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'graduation_stole_alt', 'label': 'graduation-stole-alt'}</t>
+          <t>graduation-stole-alt</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'blue',_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'blue', 'label': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'red', 'label': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'gold',_'label':_'gold'}</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'gold', 'label': 'gold'}</t>
+          <t>gold</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'silver',_'label':_'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'silver', 'label': 'silver'}</t>
+          <t>silver</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'black',_'label':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'black', 'label': 'black'}</t>
+          <t>black</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'gray',_'label':_'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'gray', 'label': 'gray'}</t>
+          <t>gray</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'white',_'label':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'white', 'label': 'white'}</t>
+          <t>white</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'other', 'label': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
